--- a/access_control_forms/008_vehicle_access_barrier_request_form--access_control_forms.xlsx
+++ b/access_control_forms/008_vehicle_access_barrier_request_form--access_control_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'gate',_'value':_'gate'}</t>
+          <t>gate</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Gate', 'value': 'Gate'}</t>
+          <t>Gate</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'boom_gate',_'value':_'boom_gate'}</t>
+          <t>boom_gate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Boom Gate', 'value': 'Boom Gate'}</t>
+          <t>Boom Gate</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'gatehouse',_'value':_'gatehouse'}</t>
+          <t>gatehouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Gatehouse', 'value': 'Gatehouse'}</t>
+          <t>Gatehouse</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'car',_'value':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Car', 'value': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'truck',_'value':_'truck'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Truck', 'value': 'Truck'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'van',_'value':_'van'}</t>
+          <t>van</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Van', 'value': 'Van'}</t>
+          <t>Van</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'ute',_'value':_'ute'}</t>
+          <t>ute</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Ute', 'value': 'Ute'}</t>
+          <t>Ute</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'trailer',_'value':_'trailer'}</t>
+          <t>trailer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Trailer', 'value': 'Trailer'}</t>
+          <t>Trailer</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'grant_access',_'value':_'grant_access'}</t>
+          <t>grant_access</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Grant Access', 'value': 'Grant Access'}</t>
+          <t>Grant Access</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'deny',_'value':_'deny'}</t>
+          <t>deny</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Deny', 'value': 'Deny'}</t>
+          <t>Deny</t>
         </is>
       </c>
     </row>
